--- a/results/Int All Data -0.9/Rando_fi_explain.xlsx
+++ b/results/Int All Data -0.9/Rando_fi_explain.xlsx
@@ -1676,466 +1676,466 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0003247834207309996</v>
+        <v>-0.0004214706669235434</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0002539820008181448</v>
+        <v>2.769565147018303e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0001247818994143301</v>
+        <v>-0.0004035544866761398</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0003386838983812734</v>
+        <v>-0.0007984108942208701</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001220726254558358</v>
+        <v>-0.0001183871540385228</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0006924683170037403</v>
+        <v>0.0004319463997651763</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0002498996477329184</v>
+        <v>-0.001572755926152248</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0009268222112021307</v>
+        <v>-0.0007015737436634384</v>
       </c>
       <c r="J3" t="n">
-        <v>8.27409963467818e-05</v>
+        <v>-0.001148332547281722</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0002190905905962171</v>
+        <v>0.0003454492486507188</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001781517847072156</v>
+        <v>0.0003310939178694194</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001581526686573043</v>
+        <v>-0.0001597900649747996</v>
       </c>
       <c r="N3" t="n">
-        <v>-9.023740146335774e-05</v>
+        <v>-0.001072821158607479</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.001027232775582131</v>
+        <v>-0.002129489221887252</v>
       </c>
       <c r="P3" t="n">
-        <v>-5.581498883004408e-05</v>
+        <v>-7.966568572667643e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00352135081950402</v>
+        <v>0.002782973689410764</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0002399105360340404</v>
+        <v>-0.0007368497623529069</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001002175516463196</v>
+        <v>-0.0005259977970201392</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0001925941618946047</v>
+        <v>0.0002435813701252465</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0001932874562830289</v>
+        <v>-0.000241067360033147</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.001796539372620561</v>
+        <v>-0.0005820923268450762</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0001487668307607693</v>
+        <v>-0.0003685933822724263</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0005600794667748744</v>
+        <v>0.0002332933576543305</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.000126392326246626</v>
+        <v>-0.0004456931482238435</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.000196235033655805</v>
+        <v>-5.065315757180719e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001898742321970209</v>
+        <v>0.001223332225597438</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0004433233383514158</v>
+        <v>-0.000774642662150179</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.0006143402608190484</v>
+        <v>0.0002577653932872548</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.00271043420805764</v>
+        <v>0.001727931138066093</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.004706459038492697</v>
+        <v>0.005551544049113581</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.001519097882529586</v>
+        <v>0.002127873428968546</v>
       </c>
       <c r="AG3" t="n">
-        <v>-3.685753070570955e-05</v>
+        <v>9.478389419042669e-05</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0005268446461605024</v>
+        <v>0.0005707343237844331</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0007543152792087139</v>
+        <v>0.00109557688474817</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.001328315311175192</v>
+        <v>0.001004066011821203</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.01446296384650431</v>
+        <v>0.01467771987704023</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.0008199712181835249</v>
+        <v>-0.000545836114366266</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.001767085683392149</v>
+        <v>0.0006477863574485464</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.0002837319499995894</v>
+        <v>0.0004679198890458347</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.0009154863584908635</v>
+        <v>-2.36090724854776e-05</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.0004310645581090811</v>
+        <v>-0.001589333914640019</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.0001423251485361054</v>
+        <v>-0.0002721744667669934</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.007152996533730938</v>
+        <v>0.00547304445530578</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0009476718192753065</v>
+        <v>-0.0003946229343361728</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.0001449470209155945</v>
+        <v>0.0003403775591013979</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.000464387185741676</v>
+        <v>0.0002445664942372172</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.757444368058145e-05</v>
+        <v>-0.0004187428110150926</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.0004880263221907066</v>
+        <v>-0.001925279056777427</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0002603260663076146</v>
+        <v>8.050105453001667e-05</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.0008164855798687665</v>
+        <v>-0.0004193733072491479</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.0005733675327402066</v>
+        <v>7.802319712546541e-05</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.003438034063897518</v>
+        <v>-0.0005320344476549254</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.002273391135478792</v>
+        <v>0.002973135583553396</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.0003883830637991715</v>
+        <v>-0.0001078427292287942</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.0002985249514070265</v>
+        <v>-0.0003179710616537634</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.0004403035193461257</v>
+        <v>0.000496467257918758</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.001011657834351059</v>
+        <v>0.0001152833447730718</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.001645883217551734</v>
+        <v>-0.001284757820730519</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.0001659879057294078</v>
+        <v>-0.0001296591695187366</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.006519572044643374</v>
+        <v>0.00403421544088284</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.001777299542939985</v>
+        <v>0.001125836187307356</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.0001502823553942621</v>
+        <v>-0.00065202887002226</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.0003868683834344111</v>
+        <v>-0.000134342086101118</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.0003996513028944071</v>
+        <v>-0.0003659854413892249</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.001151708512474571</v>
+        <v>0.0005693055002177416</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0.00072707791136293</v>
+        <v>-0.0003934116644758602</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.001114652557021256</v>
+        <v>-0.000199667399368898</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0003185987544505965</v>
+        <v>-0.001126542674578276</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.0002910715042843481</v>
+        <v>-0.0001869627334215684</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0001354040720006477</v>
+        <v>0.0004688959417148242</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.0005560057946387886</v>
+        <v>-0.0003055127513311783</v>
       </c>
       <c r="BV3" t="n">
-        <v>-7.937101339433147e-05</v>
+        <v>-0.0008120782876105636</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.723733452436261e-05</v>
+        <v>2.421411054044698e-05</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0.0009968228719136698</v>
+        <v>-0.0001738472514668788</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.0003363369420429519</v>
+        <v>-0.000334922129232581</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0002573912433943792</v>
+        <v>-0.0005883296004560676</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0.0004304000090690951</v>
+        <v>-0.0003972769478447469</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0.0005645431683125224</v>
+        <v>-0.000387084486783641</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.0007377255651789295</v>
+        <v>0.00022313746957213</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.0009420045315296855</v>
+        <v>-0.0002074058711731997</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.0005303557795642135</v>
+        <v>-0.0002378627246874565</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.0001857175698899016</v>
+        <v>-0.0002364718284449896</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.0002968843075247529</v>
+        <v>-0.0005536857841866915</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0003881194619875494</v>
+        <v>-3.652827580562178e-05</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.00118038246250824</v>
+        <v>-0.0003988781637687611</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-3.178838472400748e-06</v>
+        <v>1.42482041288361e-05</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.0007421330922631808</v>
+        <v>0.000379264752419961</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0.001041552770784487</v>
+        <v>-0.002367905254600582</v>
       </c>
       <c r="CM3" t="n">
-        <v>4.327262568049942e-05</v>
+        <v>1.17838610508925e-05</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.000557806853941104</v>
+        <v>0.0004830257379611892</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.001135637170818815</v>
+        <v>0.0004117254488994382</v>
       </c>
       <c r="CP3" t="n">
-        <v>-0.0002033095214929248</v>
+        <v>3.034745232058377e-05</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-1.440099910085763e-05</v>
+        <v>-0.0006273443087800312</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.0005106627047679635</v>
+        <v>-0.0004012387743399169</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0.00219167972292881</v>
+        <v>-0.002678165583269602</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0.001601586145378117</v>
+        <v>-0.003108116817282488</v>
       </c>
       <c r="CU3" t="n">
-        <v>-1.836177031785067e-05</v>
+        <v>-9.155072726416469e-05</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.0001672829698431855</v>
+        <v>-0.0001211306047487026</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.001698636200485785</v>
+        <v>-0.00211203005361006</v>
       </c>
       <c r="CY3" t="n">
-        <v>-0.001098722885339431</v>
+        <v>-0.002734387123792079</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.0001817239251062519</v>
+        <v>0.0001240630828823541</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.0002530742910543993</v>
+        <v>-9.260258873631799e-05</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.0006947350928239238</v>
+        <v>0.0004277264123946944</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0.001890184107297693</v>
+        <v>-0.002992960967842104</v>
       </c>
       <c r="DD3" t="n">
-        <v>7.296067952729856e-05</v>
+        <v>6.383201402528238e-05</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.001042934109228695</v>
+        <v>-4.154110277145961e-05</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.00145233902975422</v>
+        <v>-0.003244972329187979</v>
       </c>
       <c r="DG3" t="n">
-        <v>9.818120878057334e-05</v>
+        <v>-0.0004711216089229453</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0.0004170381708797965</v>
+        <v>-0.001438939857520537</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.000194141326435685</v>
+        <v>-0.0007678111561100687</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.0003863654317225886</v>
+        <v>-0.002114909101264295</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0.0003047785156855842</v>
+        <v>-0.000537846135464899</v>
       </c>
       <c r="DL3" t="n">
-        <v>4.392207258764213e-05</v>
+        <v>9.688314335787431e-05</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0.0006209842306735902</v>
+        <v>-7.143279127886371e-05</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.00105813560164085</v>
+        <v>-0.0001299065377222508</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.0004882328401717594</v>
+        <v>-0.002053443116677101</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.00120970721047929</v>
+        <v>-0.001279378434598323</v>
       </c>
       <c r="DQ3" t="n">
-        <v>3.033645140506747e-05</v>
+        <v>-0.0001434619840434748</v>
       </c>
       <c r="DR3" t="n">
-        <v>-1.054280333986579e-05</v>
+        <v>5.252588363678701e-05</v>
       </c>
       <c r="DS3" t="n">
-        <v>-3.768956260393308e-05</v>
+        <v>-6.537153821193685e-05</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0.0007408080520930416</v>
+        <v>-0.001781164438676498</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.0004156873588977372</v>
+        <v>-0.001690418558379776</v>
       </c>
       <c r="DV3" t="n">
-        <v>2.96033155713471e-06</v>
+        <v>-2.947244326555465e-06</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.0001818037450829923</v>
+        <v>0.000392248352267549</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.0002949018338545739</v>
+        <v>-0.0004186021479709745</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.0006881009956148953</v>
+        <v>-0.001438407008724787</v>
       </c>
       <c r="DZ3" t="n">
-        <v>6.307120716318338e-05</v>
+        <v>-7.123062897177457e-05</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.00104024412063482</v>
+        <v>-0.0008558368690388318</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.001290567855625971</v>
+        <v>-0.0006177755179963974</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0.000211238889042803</v>
+        <v>-0.0001886556963324071</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.000471462900369749</v>
+        <v>-0.0004832732629827063</v>
       </c>
       <c r="EE3" t="n">
-        <v>5.303007299175322e-05</v>
+        <v>-1.11433914506498e-05</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.000454601929464018</v>
+        <v>-0.0003716291858773213</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.0004097111219705031</v>
+        <v>8.375926116021336e-05</v>
       </c>
       <c r="EH3" t="n">
-        <v>-5.901386813665477e-05</v>
+        <v>-0.0001908111409388158</v>
       </c>
       <c r="EI3" t="n">
-        <v>-4.824573623691264e-05</v>
+        <v>-0.0001047616124954776</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.0003123288960029647</v>
+        <v>-0.0002384007616126782</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.0007193881432179327</v>
+        <v>-0.001113777468147383</v>
       </c>
       <c r="EL3" t="n">
-        <v>-1.606256588546626e-06</v>
+        <v>-2.152872507410697e-05</v>
       </c>
       <c r="EM3" t="n">
-        <v>1.349354619138986e-06</v>
+        <v>0.0001614613077880845</v>
       </c>
       <c r="EN3" t="n">
-        <v>-5.151591651540555e-05</v>
+        <v>8.827626226818542e-05</v>
       </c>
       <c r="EO3" t="n">
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.0001448667520184355</v>
+        <v>2.546328016111655e-05</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-3.68105040106237e-05</v>
+        <v>-0.0001155309162504059</v>
       </c>
       <c r="ER3" t="n">
-        <v>-0.0001179830709044416</v>
+        <v>-4.192322011143169e-05</v>
       </c>
       <c r="ES3" t="n">
-        <v>-6.979482409502635e-06</v>
+        <v>-1.483463716051236e-05</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.0001699011958277941</v>
+        <v>-0.0007948675284195416</v>
       </c>
       <c r="EU3" t="n">
-        <v>-1.240567308234857e-05</v>
+        <v>-0.0003762564115724188</v>
       </c>
       <c r="EV3" t="n">
-        <v>1.686788004740202e-05</v>
+        <v>5.41255790005868e-05</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0.0004890312015970522</v>
+        <v>-0.0007174342285012502</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.000259276937994205</v>
+        <v>-0.0005440785682040184</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.0002840116962012862</v>
+        <v>1.60723094410953e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2145,466 +2145,466 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003199168470011534</v>
+        <v>0.005545538979516106</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001772358598821649</v>
+        <v>0.001202882105381153</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001231471119638742</v>
+        <v>0.00112079952230389</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001515429768654828</v>
+        <v>0.001956910208015329</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000410728678009443</v>
+        <v>0.0008702219991706486</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00269349024863396</v>
+        <v>0.002179532039928901</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0008628064975261233</v>
+        <v>0.003645067183967711</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00462613115828963</v>
+        <v>0.003561054935572614</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002457734852655216</v>
+        <v>0.002433284250904225</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0005704081866562467</v>
+        <v>0.001116755614451973</v>
       </c>
       <c r="L4" t="n">
-        <v>0.000762179393522948</v>
+        <v>0.0003891798261201719</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001702656357698645</v>
+        <v>0.001753609773950066</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004426307563309973</v>
+        <v>0.005231866283033917</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005005824515358477</v>
+        <v>0.005026829469708949</v>
       </c>
       <c r="P4" t="n">
-        <v>0.000615170155043419</v>
+        <v>0.001212202894742609</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.008933490925960975</v>
+        <v>0.005640132523551027</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001175664527549676</v>
+        <v>0.001613833526582826</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00486771964611758</v>
+        <v>0.00577041496423707</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0005829349649985922</v>
+        <v>0.00111588883901774</v>
       </c>
       <c r="U4" t="n">
-        <v>0.00098631132977318</v>
+        <v>0.001138733605254929</v>
       </c>
       <c r="V4" t="n">
-        <v>0.003154780368282702</v>
+        <v>0.005798596641137359</v>
       </c>
       <c r="W4" t="n">
-        <v>0.00182958857846178</v>
+        <v>0.001535844746221393</v>
       </c>
       <c r="X4" t="n">
-        <v>0.003861100946884237</v>
+        <v>0.00585324769954731</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0008305751276446808</v>
+        <v>0.001337827304726869</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002638841239854462</v>
+        <v>0.003298682869774746</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002687815297552294</v>
+        <v>0.002455292914255284</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.001144897886813422</v>
+        <v>0.00150610959904125</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.003205176386103894</v>
+        <v>0.0011373757175076</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.006921733949852463</v>
+        <v>0.00572324936025211</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.007155407865229265</v>
+        <v>0.006824433293015773</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.004470132697368861</v>
+        <v>0.004026995275027475</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0008192840291851929</v>
+        <v>0.001190450246986897</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.001225796490743887</v>
+        <v>0.001203073488260051</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.00217125300858758</v>
+        <v>0.002904426839660329</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.006709569908755204</v>
+        <v>0.008061616930222193</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01548673822383921</v>
+        <v>0.009750201400306616</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001374322020416168</v>
+        <v>0.001607432154213616</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.005059568047565902</v>
+        <v>0.004203150880601697</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.001551241724254497</v>
+        <v>0.001589264204991607</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.005105227641508922</v>
+        <v>0.003038748545484174</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.002058968562232903</v>
+        <v>0.001969476418009466</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.001956267475484421</v>
+        <v>0.00237777474089967</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.00825473423335746</v>
+        <v>0.006236422729535384</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.00246732774630262</v>
+        <v>0.001884345703282988</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.003511742948633864</v>
+        <v>0.00269948657701568</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.002322857313464891</v>
+        <v>0.002268473237322375</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.002426027846099463</v>
+        <v>0.001844464236977507</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.001863168368729859</v>
+        <v>0.001627245054581281</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.001072351620552929</v>
+        <v>0.0016185765551685</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.002162089918433057</v>
+        <v>0.001452045116800501</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.0038117094489195</v>
+        <v>0.003255674650477257</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.004530398372983752</v>
+        <v>0.00441367506581106</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.007950499188288065</v>
+        <v>0.004863007514527032</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0006442915667180425</v>
+        <v>0.0008135766140105849</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0006351976237427551</v>
+        <v>0.0006387933808028196</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.001958867885425133</v>
+        <v>0.003131986646763106</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.004144720885184561</v>
+        <v>0.00375220699153822</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.006206026754513707</v>
+        <v>0.004194961440668169</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.001594945038765817</v>
+        <v>0.001640988366236584</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.009956754490054188</v>
+        <v>0.008413204993151388</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.002705779450188707</v>
+        <v>0.002859836254261539</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.00364041637912087</v>
+        <v>0.0025630274036786</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0008862298689173787</v>
+        <v>0.0006436846066464985</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.001726711033289463</v>
+        <v>0.001838142944089222</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.005352771838655213</v>
+        <v>0.00255355921322316</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.002246089235892866</v>
+        <v>0.003250591107997765</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.001777249206972905</v>
+        <v>0.001600210352158341</v>
       </c>
       <c r="BQ4" t="n">
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.002675023870689886</v>
+        <v>0.002761251062895156</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.001196727732448954</v>
+        <v>0.001709340739585524</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001033048919123826</v>
+        <v>0.001906661479080763</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.002302256127129204</v>
+        <v>0.001803473136512306</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.00207160423035973</v>
+        <v>0.00175778949138569</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0001518248378613744</v>
+        <v>4.97718130792018e-05</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.001876519840301544</v>
+        <v>0.001799156793509762</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.001617547600394877</v>
+        <v>0.003513038488749909</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.001446672822552831</v>
+        <v>0.004038545876745772</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.000809975325900083</v>
+        <v>0.001544952692346233</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.001834378155921403</v>
+        <v>0.002487942583833749</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.002204511039528993</v>
+        <v>0.001871975922190491</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.002008453491849847</v>
+        <v>0.001788407309871517</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.002077165102329695</v>
+        <v>0.003872421572084043</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.001486001466654053</v>
+        <v>0.003044023502758524</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.001467533998839747</v>
+        <v>0.001307299134060213</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.00134722785559418</v>
+        <v>0.001204516996673903</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.001502589890341658</v>
+        <v>0.00174685750347067</v>
       </c>
       <c r="CJ4" t="n">
-        <v>4.779018327377397e-05</v>
+        <v>8.174710961824226e-05</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.001371364627108006</v>
+        <v>0.001967396598739886</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.006630583614904986</v>
+        <v>0.006365924121471093</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.001310571953775371</v>
+        <v>0.002196292735162707</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.00141328890296212</v>
+        <v>0.001270486946233416</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.001969640457724831</v>
+        <v>0.001901535952317827</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0002976484661278887</v>
+        <v>0.0003050353671747763</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.002161863157260142</v>
+        <v>0.003421724085139397</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.00527506805797017</v>
+        <v>0.004227021149004961</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.006382329536098567</v>
+        <v>0.005471177350073375</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.00276932486290324</v>
+        <v>0.006936661294267337</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0004622453372477053</v>
+        <v>0.0003190441111152799</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0004308118988832279</v>
+        <v>0.0004779438089453653</v>
       </c>
       <c r="CW4" t="n">
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.005136181380564825</v>
+        <v>0.006404240723285265</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.006669324253048788</v>
+        <v>0.00607812190113081</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0003392905987201847</v>
+        <v>0.0005175600640163697</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0002643146122631269</v>
+        <v>0.0005676612596626717</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.002346952035137911</v>
+        <v>0.002708208918532508</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.00614476885662369</v>
+        <v>0.006959672549666209</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0003284499262160676</v>
+        <v>0.0006035263373131442</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.002616591461210442</v>
+        <v>0.001646921816784948</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.005642647343499944</v>
+        <v>0.007827324880513881</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.001119199943592632</v>
+        <v>0.001108549025912715</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.002018100266920075</v>
+        <v>0.002867383697290784</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.002890894658346146</v>
+        <v>0.002821914167389054</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.002823978879347521</v>
+        <v>0.003761635679609264</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.001495321622461345</v>
+        <v>0.001956572802456732</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0001900840968172971</v>
+        <v>0.000210398610624185</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0009612816956643234</v>
+        <v>0.0007968232565103058</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.003015009591812449</v>
+        <v>0.002522125161953662</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.003123520170151389</v>
+        <v>0.003386547448854535</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.002056530463927979</v>
+        <v>0.003051335049580592</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0008352757726847203</v>
+        <v>0.000331713632583809</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0003045959027652792</v>
+        <v>0.0007212354281213835</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0002731256699968813</v>
+        <v>0.0005167732123611401</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.00238229067643545</v>
+        <v>0.004340372516502951</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.002650475862731047</v>
+        <v>0.002969059358630767</v>
       </c>
       <c r="DV4" t="n">
-        <v>9.361390349818565e-06</v>
+        <v>9.320004892924347e-06</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0002880906152144512</v>
+        <v>0.0007817093542439576</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.001407170115916582</v>
+        <v>0.001911599818309579</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.00332784521197711</v>
+        <v>0.004055219485623113</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.000535261740930483</v>
+        <v>0.0002382963828465361</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.002024814032571987</v>
+        <v>0.002001122815125599</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.00187264351067158</v>
+        <v>0.002175785832950939</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.0008795060639365399</v>
+        <v>0.001295315117429653</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.00093744491716261</v>
+        <v>0.001024688667851202</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0001281745179313664</v>
+        <v>0.0001001883681749361</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.0008382499758391141</v>
+        <v>0.001116433864309163</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.0009406162897747685</v>
+        <v>0.001029281893046216</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0006837893724928526</v>
+        <v>0.0005746355588957463</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.001577961878967396</v>
+        <v>0.001835823383099491</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.001114809559338466</v>
+        <v>0.001091432027462306</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.0009871514955281477</v>
+        <v>0.0009659165824816938</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.0001599931900284225</v>
+        <v>4.344865530323601e-05</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.000173022921895242</v>
+        <v>0.0003435989075967085</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0002081553897674095</v>
+        <v>0.0001987800125367792</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0002931192982102533</v>
+        <v>0.0003811682230671966</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.000934079749061186</v>
+        <v>0.001416467262702637</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.0002850772148765768</v>
+        <v>0.0002156350245564027</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0001459552968739851</v>
+        <v>0.0003073523544157489</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.001542783243074963</v>
+        <v>0.001332818323946847</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.001529371953675425</v>
+        <v>0.001685034388747268</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0003214537069385377</v>
+        <v>0.000224410867733048</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.001144975385102203</v>
+        <v>0.001257731763921658</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.001203816350236674</v>
+        <v>0.000980459157904931</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.0007932173689076431</v>
+        <v>0.001030756658780145</v>
       </c>
     </row>
     <row r="5">
@@ -2614,466 +2614,466 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.007854523227383869</v>
+        <v>-0.01503667481662596</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.002475685234305969</v>
+        <v>-0.001546698393813162</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.001065496709495417</v>
+        <v>-0.002383863080684623</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.001558679706601462</v>
+        <v>-0.005415803492157445</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0005651397977393891</v>
+        <v>-0.001769389560601542</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.003566165635131202</v>
+        <v>-0.003102475712942643</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.001650366748166265</v>
+        <v>-0.009963325183374127</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.005623471882640585</v>
+        <v>-0.00837408312958442</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.002852203975799516</v>
+        <v>-0.005091770278271179</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.001060842433697373</v>
+        <v>-0.00172516359309931</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.001061633736360912</v>
+        <v>-0.0001183782184078108</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.001890694239291046</v>
+        <v>-0.002852203975799483</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.006483126110124327</v>
+        <v>-0.008498991645059073</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.01283618581907091</v>
+        <v>-0.01408924205378976</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.0008552049542907336</v>
+        <v>-0.00174607872151521</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.01438255231358684</v>
+        <v>-0.005865016209843843</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.00156203949307403</v>
+        <v>-0.003850855745721293</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.01057457212713936</v>
+        <v>-0.01641198044009783</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0009141846063107972</v>
+        <v>-0.00116136919315406</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.00130254588513915</v>
+        <v>-0.002444374804136618</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.009382640586797053</v>
+        <v>-0.01592298288508561</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.002919492774992627</v>
+        <v>-0.00446210268948658</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.003270171149144241</v>
+        <v>-0.007457212713936479</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.001716992303137954</v>
+        <v>-0.004114860864416847</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.006041850869437126</v>
+        <v>-0.004450338933097597</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.001123595505618025</v>
+        <v>-0.001344743276283655</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.001903628792385448</v>
+        <v>-0.003568268947213138</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.003006189213085808</v>
+        <v>-0.001598105948505457</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.007457212713936423</v>
+        <v>-0.006841639634326113</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.007823960880195602</v>
+        <v>-0.004431540342298324</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.004676039119804409</v>
+        <v>-0.004431540342298324</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.001283618581907098</v>
+        <v>-0.00138288677614522</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.001831610044313181</v>
+        <v>-0.0008567208271787252</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.001154446177847168</v>
+        <v>-0.001679929266136193</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.01185819070904645</v>
+        <v>-0.01074898151049826</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.006104393984075474</v>
+        <v>-0.001297552344441111</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.002706722189173072</v>
+        <v>-0.003353180821059198</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.004017725258493432</v>
+        <v>-0.004512691946098402</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.00371571807726333</v>
+        <v>-0.001887348864641658</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.006968215158924218</v>
+        <v>-0.004736530491415048</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.003361858190709033</v>
+        <v>-0.005249189029784673</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.002933985330073341</v>
+        <v>-0.005208641609943787</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.005867970660146704</v>
+        <v>-0.003698044009779988</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.001687388987566607</v>
+        <v>-0.003066941905042719</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.004836193447737946</v>
+        <v>-0.004203670811130833</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.002633915359573879</v>
+        <v>-0.003270171149144296</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.004126142057176574</v>
+        <v>-0.003418803418803451</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.001130806845965771</v>
+        <v>-0.004024859425865635</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.001444149720011834</v>
+        <v>-0.002535292422932878</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.001329394387001492</v>
+        <v>-0.003025672371638177</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.0084352078239609</v>
+        <v>-0.008129584352078289</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.0009141846063107862</v>
+        <v>-0.006782659982306061</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.004335004423473887</v>
+        <v>-0.002506635210852215</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.0006192863462105236</v>
+        <v>-0.0009168704156479523</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.001270310192023627</v>
+        <v>-0.001238572692421069</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.004235090751944714</v>
+        <v>-0.005308168681804726</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.004203670811130855</v>
+        <v>-0.006428782070185757</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.01858190709046457</v>
+        <v>-0.01262224938875307</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.001992861392028511</v>
+        <v>-0.003004164187983283</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.003958641063515578</v>
+        <v>-0.003774697729283349</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.002447655558832184</v>
+        <v>-0.003422982885085613</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.007854523227383881</v>
+        <v>-0.004825340438129056</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.002189997040544556</v>
+        <v>-0.001272565847883966</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.00284229828850856</v>
+        <v>-0.004187041564792193</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.008618581907090483</v>
+        <v>-0.001716068642745683</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.004332449160035423</v>
+        <v>-0.00535820011841327</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.00452111838191549</v>
+        <v>-0.00432208407341621</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.002414425427872846</v>
+        <v>-0.006265281173594183</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.001584557764333105</v>
+        <v>-0.002287684111563759</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.0009748892171344336</v>
+        <v>-0.002042628774422717</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.002650532987611687</v>
+        <v>-0.003572547790661218</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.003837001784651983</v>
+        <v>-0.004105296145408954</v>
       </c>
       <c r="BW5" t="n">
-        <v>-8.84694780300621e-05</v>
+        <v>-6.112469437653534e-05</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.003985722784057078</v>
+        <v>-0.004614914425427896</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.00240249609984402</v>
+        <v>-0.006769037919147569</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.001686889612311337</v>
+        <v>-0.00793368857312019</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.002008862629246744</v>
+        <v>-0.002745709828393128</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.003037452079032743</v>
+        <v>-0.005012224938875343</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.004481353807583788</v>
+        <v>-0.003831748775569022</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.004351687388987569</v>
+        <v>-0.003791914760263226</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.003493191237418591</v>
+        <v>-0.00435168738898758</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.002545885139135606</v>
+        <v>-0.005978100029594558</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.003656738425243278</v>
+        <v>-0.002350360388592909</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.001385204833480747</v>
+        <v>-0.002506112469437671</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.003242117787031496</v>
+        <v>-0.003728913879846107</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-6.267627702913892e-05</v>
+        <v>-0.0001487209994050942</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.001686889612311326</v>
+        <v>-0.003088923556942236</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.01921255180580225</v>
+        <v>-0.01983422143280047</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0.002811482687185607</v>
+        <v>-0.005593370819769161</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.001242971293282036</v>
+        <v>-0.0006581009088060142</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0.002426753477360189</v>
+        <v>-0.003669724770642202</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.000710269310446865</v>
+        <v>-0.0005308168681804393</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.003978779840848834</v>
+        <v>-0.009440662918023068</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.01190053285968028</v>
+        <v>-0.009085528262799635</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.02007104795737125</v>
+        <v>-0.01749555950266429</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.008614564831261096</v>
+        <v>-0.01681468324452339</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0.0006806747558449122</v>
+        <v>-0.000589796520200514</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0.001090480400825289</v>
+        <v>-0.001094785364448314</v>
       </c>
       <c r="CW5" t="n">
         <v>0</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0.01515689757252813</v>
+        <v>-0.01950858496151568</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.01805802249851983</v>
+        <v>-0.01853167554766134</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.001011302795954738</v>
+        <v>-0.001222493887530596</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0.0002750611246943868</v>
+        <v>-0.0008863080684596957</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0.002989050014797312</v>
+        <v>-0.00633323468481799</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0.01847246891651866</v>
+        <v>-0.0199822380106572</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0.0003545051698670587</v>
+        <v>-0.0009168704156479413</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0.003107428233205134</v>
+        <v>-0.003906481207457835</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.01545293072824158</v>
+        <v>-0.02448194197750148</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0.001742053789731057</v>
+        <v>-0.002597799511002486</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.00444049733570161</v>
+        <v>-0.005891059798697451</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.006453471622010987</v>
+        <v>-0.008297320656871244</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.008163866784556485</v>
+        <v>-0.01220159151193637</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0.003654582964927833</v>
+        <v>-0.005717653993516081</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0.0003249630723781372</v>
+        <v>-0.0004073958006894363</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0.002322738386308065</v>
+        <v>-0.001390944066291777</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0.007771858351613858</v>
+        <v>-0.004155614500442118</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.008655562165377695</v>
+        <v>-0.007844878626406149</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0.005026769779892892</v>
+        <v>-0.005743043220840749</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.000825715128280713</v>
+        <v>-0.0008582420834566285</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.000407395800689403</v>
+        <v>-0.001213376738680061</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.0006240249609984705</v>
+        <v>-0.001216848673946969</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.004937537180249829</v>
+        <v>-0.01101243339253997</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0.002260559190957723</v>
+        <v>-0.008200118413262269</v>
       </c>
       <c r="DV5" t="n">
-        <v>0</v>
+        <v>-2.947244326555465e-05</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0.0002974419988102106</v>
+        <v>-0.0006418092909535877</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.001152141802067963</v>
+        <v>-0.004379141457793156</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0.0071088637715645</v>
+        <v>-0.01092362344582595</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.0008271787296898036</v>
+        <v>-0.000503107428233196</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.004494382022471932</v>
+        <v>-0.005275567344532895</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.004462102689486558</v>
+        <v>-0.005195599022004904</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0.001555747623163395</v>
+        <v>-0.002948982601002581</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0.001004431314623333</v>
+        <v>-0.002693104468777718</v>
       </c>
       <c r="EE5" t="n">
-        <v>-0.0001179593040400828</v>
+        <v>-0.0002063071028588825</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0.0004431314623338234</v>
+        <v>-0.001974302726418031</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.001210025929127101</v>
+        <v>-0.001562039493073997</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0.00149812734082404</v>
+        <v>-0.001210025929127068</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.002099655280476287</v>
+        <v>-0.003315571343990531</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.002381698527107434</v>
+        <v>-0.002914446881855193</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0.00272641805076772</v>
+        <v>-0.002420051858254113</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0.0003745318352060378</v>
+        <v>-9.401441554370837e-05</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0.0003241968759210456</v>
+        <v>-0.0002368265245707768</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0.0005762028233938787</v>
+        <v>-0.0001248049921996675</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.0003241968759210567</v>
+        <v>-0.0004143237644273379</v>
       </c>
       <c r="EQ5" t="n">
-        <v>-0.001152405646787702</v>
+        <v>-0.003025672371638166</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.0009136457412319942</v>
+        <v>-0.0005599764220454384</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.0002663509914175743</v>
+        <v>-0.0005640864932622836</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0.00227474150664706</v>
+        <v>-0.003666562206204948</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.002688330871491962</v>
+        <v>-0.003415857098088349</v>
       </c>
       <c r="EV5" t="n">
-        <v>-0.0004164187983342838</v>
+        <v>-0.0001776198934280826</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0.002601065496709454</v>
+        <v>-0.002689486552567277</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.00232832301797824</v>
+        <v>-0.00192421551213735</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.00172516359309931</v>
+        <v>-0.002169926650366771</v>
       </c>
     </row>
     <row r="6">
@@ -3083,466 +3083,466 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.001202391454495114</v>
+        <v>-0.0004424792659006249</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.001662877080756298</v>
+        <v>-0.0006852994912157795</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0009280249571841149</v>
+        <v>-0.001032164703866573</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0008780363031360594</v>
+        <v>-0.001326725005057045</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0001064319545697884</v>
+        <v>-0.0003279211080696204</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0004629304687155084</v>
+        <v>-0.001242619264672784</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0009229291891343249</v>
+        <v>-0.002664368196689088</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0003072394654223321</v>
+        <v>-0.001685526351883257</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.001943407037441031</v>
+        <v>-0.002390657424049774</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0005392068201669264</v>
+        <v>-0.0003288323362419216</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0002162541449959393</v>
+        <v>0.0001062154845744595</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0009546810787040005</v>
+        <v>-0.001369783129148025</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0022714091998674</v>
+        <v>-0.00560182315605583</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.00207414822679943</v>
+        <v>-0.004151996192602134</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0004364805549506828</v>
+        <v>-0.0006489070296655825</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0008256808854333414</v>
+        <v>-0.0007869212848277296</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.0007747196150770935</v>
+        <v>-0.001035269230130889</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0002613312585324546</v>
+        <v>-0.0003892358225537629</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0005668671734644748</v>
+        <v>-0.0006056261128011498</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0004600815182717155</v>
+        <v>-0.001085844286154272</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.002429095374256973</v>
+        <v>-0.0002808349107269348</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0008148014334428549</v>
+        <v>-0.0001549341446057423</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.0007974835847366968</v>
+        <v>-0.001977077946709785</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.0005665192634293409</v>
+        <v>-0.0003322642077702553</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.001070513934684908</v>
+        <v>-0.003128513954739127</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0005547407720299741</v>
+        <v>-0.0006521146866819011</v>
       </c>
       <c r="AB6" t="n">
-        <v>-6.088035409004545e-05</v>
+        <v>-0.001851769283372892</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.0008878482310367336</v>
+        <v>-0.0002880354505169769</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.0003254094921621459</v>
+        <v>-0.002293713248519974</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.00158675211906838</v>
+        <v>0.002630792433095269</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.001171895304478251</v>
+        <v>9.688922045189281e-05</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0004828194895898446</v>
+        <v>-0.0004102961252180653</v>
       </c>
       <c r="AH6" t="n">
-        <v>-7.61333919899937e-05</v>
+        <v>-0.0003290247480823211</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.000877701292020247</v>
+        <v>-0.0004957620388000405</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-7.466085390595012e-05</v>
+        <v>-0.003455517947987882</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.001149196204105404</v>
+        <v>0.007692822788046802</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.001696974102975563</v>
+        <v>-0.001441255293287636</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.002854604744991307</v>
+        <v>-0.002864625710853994</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.0007594038594334912</v>
+        <v>-0.0005420416694707969</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.0008954656610049682</v>
+        <v>-0.001103288070789632</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.001608844245227536</v>
+        <v>-0.002525565124410231</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.001418079636151739</v>
+        <v>-0.0006424110460330368</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.002064357915087314</v>
+        <v>0.001676610937382872</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.0004956563324696849</v>
+        <v>-0.00167966603685597</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.002770489910822807</v>
+        <v>-0.0009699712984792358</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.001122612772448745</v>
+        <v>-0.001413757277299529</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.0006201488256123155</v>
+        <v>-0.002120714183917313</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.0007253483640084462</v>
+        <v>-0.003193900393230156</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0001382498360598672</v>
+        <v>-0.0009028376078979022</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.0004347793777725262</v>
+        <v>-0.001091411055504865</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.0002061407784423736</v>
+        <v>-0.0004499184533851646</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.527986051975634e-05</v>
+        <v>-0.003255399878916509</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.002161179452629253</v>
+        <v>-0.001303842170495248</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.0001035022554372877</v>
+        <v>-0.0005689083193921224</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0006936299345445984</v>
+        <v>-0.0007226344505879805</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.001533196036013895</v>
+        <v>-0.0008842675690609897</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.001861218102982037</v>
+        <v>-0.002075315196515901</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.001178751968639111</v>
+        <v>-0.0015625632130081</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.0008945804179795042</v>
+        <v>-0.0009220807057729401</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.002462005138581697</v>
+        <v>-0.002392422429466134</v>
       </c>
       <c r="BJ6" t="n">
-        <v>5.948983849241307e-05</v>
+        <v>-0.0007090890254036642</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.001034705368431529</v>
+        <v>-0.00297083714349336</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0005941653396473428</v>
+        <v>-0.0002509913418342558</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.001153754858293679</v>
+        <v>-0.0008865405431022627</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.001635414835590107</v>
+        <v>-0.001327445492490889</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.00178275801454019</v>
+        <v>-0.003172582987903394</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.001693351943104246</v>
+        <v>-0.0003476754270730992</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.0008947600121964216</v>
+        <v>-0.002072006644693128</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.001029978609521698</v>
+        <v>-0.001333859172178395</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0006226872406380424</v>
+        <v>-0.0006899145157154646</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.0008658772682806903</v>
+        <v>-0.0009293635051582372</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.0008455071912982587</v>
+        <v>-0.001476432752385265</v>
       </c>
       <c r="BW6" t="n">
-        <v>-2.956402676785319e-05</v>
+        <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.002213907901938472</v>
+        <v>-0.0007396933794314609</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.001864784976342798</v>
+        <v>-0.002248525356600453</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.0006026473253513021</v>
+        <v>-0.003364670393665586</v>
       </c>
       <c r="CA6" t="n">
-        <v>-0.0009211398769458284</v>
+        <v>-0.001664200966399218</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.001839610497104785</v>
+        <v>-0.002104699989463674</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.002398204664979667</v>
+        <v>-0.000196753153736276</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.001777441546329714</v>
+        <v>-0.0009548125904080912</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.001654706390475774</v>
+        <v>-0.003051975362045598</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.00090137494464681</v>
+        <v>-0.002244637490759907</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.0007638857858764032</v>
+        <v>-0.001354623111431533</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0002750611246943758</v>
+        <v>-0.0006812117702472975</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.002206705158918379</v>
+        <v>-0.0009416803638437777</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-3.032039904168893e-05</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.000169710246124638</v>
+        <v>-0.0004015586673560611</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.0008405280205098647</v>
+        <v>-0.001957497615004208</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.0003751941373018846</v>
+        <v>-0.0003193629849797597</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.0002586963897260209</v>
+        <v>-0.0002588474385410211</v>
       </c>
       <c r="CO6" t="n">
-        <v>-0.0003708720536098747</v>
+        <v>-0.0003659282118465723</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.0003174468693086602</v>
+        <v>-0.0001064843188657877</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.001582889756836783</v>
+        <v>-0.0009529159948435479</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.002547065021799455</v>
+        <v>-0.00153996992611381</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0.001232031336755696</v>
+        <v>-0.002874856967133585</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0.002288916043274866</v>
+        <v>-0.004590919965918821</v>
       </c>
       <c r="CU6" t="n">
-        <v>-0.0002384107181126277</v>
+        <v>-0.0001974455159908462</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0.0003398259210704024</v>
+        <v>-0.0003754758186801072</v>
       </c>
       <c r="CW6" t="n">
         <v>0</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0.002758058014228943</v>
+        <v>-0.002365424775397795</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0.001209501038242222</v>
+        <v>-0.003052321753131762</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.0003003614688969814</v>
+        <v>3.120124804992796e-05</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.0001199644309813425</v>
+        <v>-0.0005761889295382905</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0.0002665149573130826</v>
+        <v>0.0002016709881878437</v>
       </c>
       <c r="DC6" t="n">
-        <v>-0.002117753948726084</v>
+        <v>-0.00593736039034779</v>
       </c>
       <c r="DD6" t="n">
-        <v>-0.0001415747805808193</v>
+        <v>-0.0002738219080655246</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0.0004032761319067546</v>
+        <v>-0.0006467251179438499</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.00333308213983754</v>
+        <v>-0.001908077472163966</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0.0006636794744886709</v>
+        <v>-0.00115030074779777</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0.001699389323887618</v>
+        <v>-0.003025520484433045</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.001239423864130967</v>
+        <v>-0.0003694785361452429</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.0002661452257731428</v>
+        <v>-0.002190367794047909</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0.0006836308573175464</v>
+        <v>-0.0006191295959324273</v>
       </c>
       <c r="DL6" t="n">
-        <v>2.963853664877114e-05</v>
+        <v>5.801686954020335e-05</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0.001233543876467028</v>
+        <v>-0.0006071562072290926</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0.002309539430217308</v>
+        <v>-0.00183736846696626</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.0003906923920855149</v>
+        <v>-0.004654624724393061</v>
       </c>
       <c r="DP6" t="n">
-        <v>-0.001743883473981064</v>
+        <v>-0.002984641676983268</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.0004952251376023426</v>
+        <v>-0.0002925254070504507</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.0002285423076138327</v>
+        <v>-4.58435207824015e-05</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.0001146088019560038</v>
+        <v>-0.0002055765698081052</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0.002071401159692796</v>
+        <v>-0.003985240986198382</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0.001599836128913648</v>
+        <v>-0.002561649893778231</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-5.892750378664323e-05</v>
+        <v>-0.0001561570493753605</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.0005434907051454941</v>
+        <v>-0.001305071449523504</v>
       </c>
       <c r="DY6" t="n">
-        <v>-0.002048110632989014</v>
+        <v>-0.002144559131562149</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.0001411353041557567</v>
+        <v>-0.0002103369809981742</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.002689813200433106</v>
+        <v>-0.001453487938545151</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.002222639520393982</v>
+        <v>-0.00159077939304651</v>
       </c>
       <c r="EC6" t="n">
-        <v>-0.0007674922744476647</v>
+        <v>-0.0009507346585998528</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0.0002082112213844467</v>
+        <v>-0.001122353689188263</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-4.440497335702065e-05</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.000148128814890458</v>
+        <v>-0.001055882676055911</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.0001324956463583771</v>
+        <v>-0.00047544932408988</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0.0002085907234480905</v>
+        <v>-0.0002697975335408692</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.001422663996663301</v>
+        <v>-0.001020383762215804</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.0009270503407453334</v>
+        <v>-0.0004355629877854511</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.001187620405750664</v>
+        <v>-0.00182783048546522</v>
       </c>
       <c r="EL6" t="n">
-        <v>0</v>
+        <v>-4.439183190292906e-05</v>
       </c>
       <c r="EM6" t="n">
-        <v>-8.202117777981465e-05</v>
+        <v>-0.0001117054241970616</v>
       </c>
       <c r="EN6" t="n">
-        <v>-5.201712871436837e-05</v>
+        <v>-2.498001805406602e-17</v>
       </c>
       <c r="EO6" t="n">
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-5.702250561936129e-05</v>
+        <v>-0.0003089573897921721</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0.0008370219194414746</v>
+        <v>-0.0004454051142449428</v>
       </c>
       <c r="ER6" t="n">
-        <v>-8.862629246676469e-05</v>
+        <v>-7.051081165778127e-05</v>
       </c>
       <c r="ES6" t="n">
-        <v>-8.643042350909847e-05</v>
+        <v>-0.0001407237796383437</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.0004049283251790214</v>
+        <v>-0.001371027437552946</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0.0004409767686583216</v>
+        <v>-0.001322360866603167</v>
       </c>
       <c r="EV6" t="n">
-        <v>-0.0001934011068640579</v>
+        <v>-8.874432097108476e-05</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0.0007502740228174764</v>
+        <v>-0.001526706734781169</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0.0009802793858999653</v>
+        <v>-0.001179032446891617</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.0008490086060633922</v>
+        <v>-0.0003349812153405629</v>
       </c>
     </row>
     <row r="7">
@@ -3552,430 +3552,430 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-7.283437199368523e-05</v>
+        <v>0.0007658944940711454</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0002445202217827847</v>
+        <v>-0.0003104280806422999</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0001769824129213726</v>
+        <v>-0.0001930380086684891</v>
       </c>
       <c r="E7" t="n">
-        <v>8.303199930739249e-05</v>
+        <v>-0.0007935536416482758</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0001084010214507325</v>
+        <v>-0.0001035503864172727</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0008281551538490695</v>
+        <v>0.001083722338793908</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.600237663713978e-05</v>
+        <v>-0.0003695130181566808</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001005401771214409</v>
+        <v>0.0001485713541260758</v>
       </c>
       <c r="J7" t="n">
-        <v>-5.296269678179978e-05</v>
+        <v>-0.001517237970175239</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0003402238657819967</v>
+        <v>0.0004427831912169944</v>
       </c>
       <c r="L7" t="n">
-        <v>1.090065854768006e-05</v>
+        <v>0.0001922502727647379</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0005045947656547756</v>
+        <v>-0.0001182602170793023</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0009843841186410519</v>
+        <v>0.0003996312157183157</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.001154393512256857</v>
+        <v>-0.001225984081081111</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.0001648231977673165</v>
+        <v>-0.0003414286128309741</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001709632738089622</v>
+        <v>0.0009756525092781188</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0005762036217067223</v>
+        <v>-0.000458798825539486</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001886100782290367</v>
+        <v>0.001056103818909493</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.000192154776460568</v>
+        <v>0.000162185351682903</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0001918668192413153</v>
+        <v>0.000202079588240095</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.0007386311228925967</v>
+        <v>0.0009298197123472295</v>
       </c>
       <c r="W7" t="n">
-        <v>0.000164736298876228</v>
+        <v>-7.38947993670358e-05</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.0003537389734099616</v>
+        <v>-0.0001030572981471856</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.110223024625157e-17</v>
+        <v>-0.0002230848828470022</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0004588931110254379</v>
+        <v>0.0001802777906111496</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0009999173568599807</v>
+        <v>0.0009014011732033811</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0003812269719918216</v>
+        <v>-0.0002863803039892199</v>
       </c>
       <c r="AC7" t="n">
-        <v>-6.368029782317651e-05</v>
+        <v>0.0003940925394015915</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.002212662180063984</v>
+        <v>0.001553183244481576</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.004587336023775345</v>
+        <v>0.004893824893011378</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.001206627504925378</v>
+        <v>0.001528374628285578</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.0002358751512190172</v>
+        <v>-0.0002063679424645137</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0009609299312048458</v>
+        <v>0.0003686644121567107</v>
       </c>
       <c r="AI7" t="n">
-        <v>-3.841352155963256e-05</v>
+        <v>0.0001482122516631712</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.001551716370254475</v>
+        <v>0.001197713919014137</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.0151540590359246</v>
+        <v>0.01775926466759826</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.0009341771062035042</v>
+        <v>-0.0004884322622686343</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.001287624946664784</v>
+        <v>-0.0004564996226513518</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1.790948262201385e-05</v>
+        <v>0.000510867326344927</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0007090260621918699</v>
+        <v>-7.798607178696179e-05</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.001010665713984932</v>
+        <v>-0.002173509903072102</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-5.957177454148918e-05</v>
+        <v>0.0001480165778567466</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.006875333306342291</v>
+        <v>0.004631840425656985</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0005389069495363829</v>
+        <v>-0.0004846494871097229</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.0002608524722784666</v>
+        <v>0.0001189979652362338</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.0003723262716768261</v>
+        <v>0.0008209721647293</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.0003744734059025645</v>
+        <v>0.0001074929461348573</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.000303683102430169</v>
+        <v>-0.002016299450312303</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0003099568019786558</v>
+        <v>0.0003119440352669145</v>
       </c>
       <c r="AY7" t="n">
-        <v>2.964712041829686e-05</v>
+        <v>-0.0004199471914952235</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.00113968608477909</v>
+        <v>0.0006301780161094006</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.002693928446793015</v>
+        <v>-0.001316198856598039</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.001515426643653678</v>
+        <v>0.002720836923364567</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0003344250999169463</v>
+        <v>-0.0002662372869091989</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.0003710980769643823</v>
+        <v>-0.0003515842320582329</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.0003847902654936231</v>
+        <v>0.0001776067519739744</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.0001047329556180311</v>
+        <v>0.001128575707063889</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.0002960594386216208</v>
+        <v>-7.405734611436454e-05</v>
       </c>
       <c r="BH7" t="n">
-        <v>-5.900572613679599e-05</v>
+        <v>0.0001033276869878585</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.003640669015657771</v>
+        <v>0.0004506821290904294</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.001191293146555983</v>
+        <v>0.001534116782078043</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.001314794027795169</v>
+        <v>0.0001189019768845834</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0.0003926498056719907</v>
+        <v>-1.586898322330498e-05</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.0005789342197316805</v>
+        <v>-4.081189493522765e-05</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.001007249485381678</v>
+        <v>-0.0004046665805674088</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.0008637319820421264</v>
+        <v>-0.0001485498012530674</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.0009901342263959833</v>
+        <v>-1.440507058484419e-05</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0.0001159028667746642</v>
+        <v>-0.0005903072232264438</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0.0005427968224597512</v>
+        <v>-0.0002569001636469837</v>
       </c>
       <c r="BT7" t="n">
-        <v>-7.281670577171107e-05</v>
+        <v>-0.0002818216724743472</v>
       </c>
       <c r="BU7" t="n">
-        <v>8.824319423818007e-05</v>
+        <v>-0.0004823761533742255</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.0005312089042721734</v>
+        <v>-0.0004573663838469244</v>
       </c>
       <c r="BW7" t="n">
-        <v>-1.440507058484974e-05</v>
+        <v>1.48016577856791e-05</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.0002959022834076841</v>
+        <v>0.0001824136908638196</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.0001031875127591064</v>
+        <v>0.000464539113322332</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0001551505292296696</v>
+        <v>8.912070007514037e-05</v>
       </c>
       <c r="CA7" t="n">
-        <v>-0.0004033419763756929</v>
+        <v>-0.0002623305753485905</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0.0008254637625894456</v>
+        <v>0.0001152173973282267</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0.0003996821947795604</v>
+        <v>0.00107859169581167</v>
       </c>
       <c r="CD7" t="n">
-        <v>-0.0008052230135182858</v>
+        <v>0.0001952679826716208</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.00086270840009246</v>
+        <v>-0.0005950824056152271</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.0005714204132339307</v>
+        <v>1.297016175986761e-05</v>
       </c>
       <c r="CG7" t="n">
-        <v>-8.913143811817845e-05</v>
+        <v>-0.0005342397122602427</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0003236182733277193</v>
+        <v>0.0001133522445772583</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0.001519467702424987</v>
+        <v>-0.0002201104768670969</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-1.440507058484974e-05</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0007410917126339899</v>
+        <v>0.0003095562593828704</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0005765692436077663</v>
+        <v>-0.001253587988916438</v>
       </c>
       <c r="CM7" t="n">
-        <v>7.456260209467991e-05</v>
+        <v>0.0002567769884178894</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0002801185816062812</v>
+        <v>-0.0001034847024773633</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.001189683821811122</v>
+        <v>0.0007263545846229458</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.0001463858526267791</v>
+        <v>1.308723057869026e-07</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0003590288301422884</v>
+        <v>0.0004592161766270142</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.001274017536763428</v>
+        <v>0.0003532044288150238</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0.0005647794597160749</v>
+        <v>-0.0003467127190834751</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0.00112805646916575</v>
+        <v>-3.669540093232402e-05</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.0001216559290491692</v>
+        <v>-4.520393959630553e-05</v>
       </c>
       <c r="CV7" t="n">
-        <v>-7.654607195591301e-05</v>
+        <v>-7.54099129482544e-05</v>
       </c>
       <c r="CW7" t="n">
         <v>0</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0.0001703528815310329</v>
+        <v>-0.0002434262563278833</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.000190668995952975</v>
+        <v>-0.0005079467546518057</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-4.420866489833197e-05</v>
+        <v>0.0002073190906187128</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.0003110911939811112</v>
+        <v>3.962855143418986e-05</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.001019294942802124</v>
+        <v>0.001053378614101574</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.0003063983167551521</v>
+        <v>0.0004085106882442069</v>
       </c>
       <c r="DD7" t="n">
-        <v>-4.422604764280358e-05</v>
+        <v>-4.424349201000988e-05</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.0006570904645476661</v>
+        <v>0.0003836445468167637</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.000288715425503655</v>
+        <v>-0.0003558080589792234</v>
       </c>
       <c r="DG7" t="n">
-        <v>7.201314298516115e-05</v>
+        <v>-0.0002827867538962414</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.000150771236542635</v>
+        <v>-0.001770928283779832</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.0001089076934747024</v>
+        <v>4.420866489828201e-05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.0001392868003723624</v>
+        <v>-0.001124702586991588</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0.0002217493854141883</v>
+        <v>4.315642276125908e-06</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.0001059868597919345</v>
+        <v>8.88510388366126e-05</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.0006506361625371826</v>
+        <v>1.457467866305407e-05</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0.0004277854273215031</v>
+        <v>-0.0001468816822435326</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.0001528117359413439</v>
+        <v>-0.001645808173741026</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0.001003725649658233</v>
+        <v>-0.002234322456607129</v>
       </c>
       <c r="DQ7" t="n">
-        <v>1.440507058484419e-05</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-2.946369027055917e-05</v>
+        <v>1.480165778569575e-05</v>
       </c>
       <c r="DS7" t="n">
-        <v>2.96033155713471e-05</v>
+        <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>-0.001165519766344936</v>
+        <v>-8.974193398837425e-05</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.0001380087175067546</v>
+        <v>-0.0008058725789732103</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.0002334089546344342</v>
+        <v>0.0003349592849786365</v>
       </c>
       <c r="DX7" t="n">
-        <v>7.270503776455883e-05</v>
+        <v>-0.000147679878403395</v>
       </c>
       <c r="DY7" t="n">
-        <v>-0.000235631114946272</v>
+        <v>-0.0002139364303178459</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-1.440507058484974e-05</v>
+        <v>1.560062402498063e-05</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.0003876462932300817</v>
+        <v>-0.000656070214848331</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.0008043300979031498</v>
+        <v>-9.068964781193123e-05</v>
       </c>
       <c r="EC7" t="n">
-        <v>-2.959455460195271e-05</v>
+        <v>0.0003764603827141777</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.0006257970270078517</v>
+        <v>-0.0001547512142570983</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>1.47449130050159e-05</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.0002110330525589121</v>
+        <v>-0.000320265744615117</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.00058969222373364</v>
+        <v>7.239133108386531e-05</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.0001222493887530485</v>
+        <v>-1.477104874446078e-05</v>
       </c>
       <c r="EI7" t="n">
-        <v>-2.680852306440883e-05</v>
+        <v>8.813871290315191e-05</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.0001608346733744881</v>
+        <v>-0.000301307829606512</v>
       </c>
       <c r="EK7" t="n">
-        <v>-0.0006745739646633441</v>
+        <v>-0.001297117775829176</v>
       </c>
       <c r="EL7" t="n">
         <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>1.477104874446078e-05</v>
+        <v>2.944104629288846e-05</v>
       </c>
       <c r="EN7" t="n">
         <v>0</v>
@@ -3984,34 +3984,34 @@
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.0001638028248225232</v>
+        <v>1.560062402495843e-05</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0.0002092834082639661</v>
+        <v>0.0001059909812788029</v>
       </c>
       <c r="ER7" t="n">
         <v>0</v>
       </c>
       <c r="ES7" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-17</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.0002761336458726338</v>
+        <v>-0.0007528560263294127</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0.0001806927801839664</v>
+        <v>-0.0003688846466051332</v>
       </c>
       <c r="EV7" t="n">
-        <v>-5.904936786617076e-05</v>
+        <v>-7.369849090834712e-05</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0.0004521094089418198</v>
+        <v>-0.0003783592152728055</v>
       </c>
       <c r="EX7" t="n">
-        <v>-0.0003995659114886363</v>
+        <v>-0.0007857196319127513</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.0001075131671203045</v>
+        <v>0.0002213439294171837</v>
       </c>
     </row>
     <row r="8">
@@ -4021,466 +4021,466 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00155565413574307</v>
+        <v>0.002007217367346375</v>
       </c>
       <c r="C8" t="n">
-        <v>0.000271013504838577</v>
+        <v>0.0006109910331857011</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0007696686829161775</v>
+        <v>0.0004002396410143661</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001725273973191088</v>
+        <v>0.0002293049347253828</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0003298020821850045</v>
+        <v>0.0004550738779365404</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002473312415642651</v>
+        <v>0.001645105085978285</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003474273802412442</v>
+        <v>0.0003948698032270603</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001407487339060745</v>
+        <v>0.001875312070922391</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001341748684340674</v>
+        <v>-0.000140877314511656</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002176233856894277</v>
+        <v>0.0008501636819346319</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005684994984775399</v>
+        <v>0.000442665122210395</v>
       </c>
       <c r="M8" t="n">
-        <v>0.001817655067848137</v>
+        <v>0.001131421522028089</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003815629932159303</v>
+        <v>0.002737044201183647</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001646594358717807</v>
+        <v>0.001321543650971868</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0002597367661993338</v>
+        <v>0.0005555335749260343</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.006873250095409351</v>
+        <v>0.007159414828450148</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0008907688685859255</v>
+        <v>5.062065871852542e-06</v>
       </c>
       <c r="S8" t="n">
-        <v>0.003364341300475138</v>
+        <v>0.001975159858598693</v>
       </c>
       <c r="T8" t="n">
-        <v>-9.429526089738682e-05</v>
+        <v>0.0006428933766686601</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001046292414491881</v>
+        <v>0.0005586585355261382</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0002210433244915655</v>
+        <v>0.001855407587903096</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0007852921989030898</v>
+        <v>0.0004131745772047196</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0005994408574115289</v>
+        <v>0.0004000626790212569</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0002265892948841025</v>
+        <v>0.0001923383763561853</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001606485573810126</v>
+        <v>0.002521444821214156</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002569223443665653</v>
+        <v>0.001974820565856353</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.001175990117079887</v>
+        <v>0.0003571086663691242</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0008971506105140109</v>
+        <v>0.001017657756973356</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.004947866733221532</v>
+        <v>0.00500195557806645</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.006296491473234675</v>
+        <v>0.006457125662024304</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.003592355352001628</v>
+        <v>0.002760176051437049</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0006019951677330964</v>
+        <v>0.0005949909260410697</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.00115566540956486</v>
+        <v>0.0009630700351350968</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.001864476162198711</v>
+        <v>0.001191948644336221</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.002600701264172689</v>
+        <v>0.005686253636136004</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.02756465380268902</v>
+        <v>0.02215292059958258</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0001896043870173808</v>
+        <v>0.0001083747928942586</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.005535641650385077</v>
+        <v>0.004733396173214941</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0004431102794873937</v>
+        <v>0.001550363307049502</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.001872537784992853</v>
+        <v>0.0008078334950237381</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0001108011069280185</v>
+        <v>-0.0001577900733552795</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.00073378450731095</v>
+        <v>0.001277505933498907</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.01126765573730374</v>
+        <v>0.008167776149248207</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.001736683085483739</v>
+        <v>0.0006290045391821208</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.001159799327441335</v>
+        <v>0.0004559829239978191</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.001226865597521601</v>
+        <v>0.00111330891110269</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0009051539444789314</v>
+        <v>0.001237938431305799</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0007914306384631392</v>
+        <v>-0.0005078498380411578</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.00104625291848014</v>
+        <v>0.0007740036362963359</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.001341075951187939</v>
+        <v>0.0002683666006658064</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.00293380399758533</v>
+        <v>0.002243526035882895</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.004234987999371919</v>
+        <v>0.0008539376588483056</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.002145285474905578</v>
+        <v>0.004913000507610582</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0004932337399586401</v>
+        <v>0.0001480449502470643</v>
       </c>
       <c r="BD8" t="n">
-        <v>9.012854676433981e-05</v>
+        <v>0.0001293798507004396</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0005141802340743462</v>
+        <v>0.002160622887201874</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.004479878846296814</v>
+        <v>0.002223826941478055</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.001135210548057938</v>
+        <v>0.0004605920876752767</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.0007695637686900903</v>
+        <v>0.0008318490042972471</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.008392267271435872</v>
+        <v>0.01032113601700113</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.003496473848466119</v>
+        <v>0.002694093375453924</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.001349738031933287</v>
+        <v>0.001366466079105919</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0001260640391775869</v>
+        <v>0.0002902982723545972</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0008658969804618028</v>
+        <v>0.0007239497382053067</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.004052582472333</v>
+        <v>0.002360191958062305</v>
       </c>
       <c r="BO8" t="n">
-        <v>7.241545762631804e-06</v>
+        <v>0.002497821633716488</v>
       </c>
       <c r="BP8" t="n">
-        <v>-0.0001992001953801087</v>
+        <v>0.0005983878719452134</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.0007474269733957594</v>
+        <v>0.0003085451219154462</v>
       </c>
       <c r="BS8" t="n">
-        <v>-0.0001861101022744588</v>
+        <v>0.0004201912792041435</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0005620347159572908</v>
+        <v>0.001404529744408159</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.00197839904900628</v>
+        <v>0.0007299225499301371</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.0004957372627332285</v>
+        <v>0.0002750611246943507</v>
       </c>
       <c r="BW8" t="n">
-        <v>2.292176039120075e-05</v>
+        <v>5.101552376701457e-05</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0003022445344548042</v>
+        <v>0.001046930410387328</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0008877589984563645</v>
+        <v>0.002176330905500107</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0005167080891626152</v>
+        <v>0.002141035871489763</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0002308818111201621</v>
+        <v>0.0007056774164817509</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0006748216642697424</v>
+        <v>0.0009524714406801359</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0004983951191788405</v>
+        <v>0.001209358578996966</v>
       </c>
       <c r="CD8" t="n">
-        <v>-0.0004351924857806666</v>
+        <v>0.0006475086589670415</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0008986377629836562</v>
+        <v>0.0006841671228616092</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0004200392402396641</v>
+        <v>0.002528535550698124</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0007152302384126647</v>
+        <v>6.652196001762922e-05</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0005727262519046178</v>
+        <v>0.0008182774864864545</v>
       </c>
       <c r="CI8" t="n">
-        <v>-0.0001826238236030564</v>
+        <v>0.0009010645824534064</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.968060641328207e-05</v>
+        <v>5.897096064782781e-05</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.00151900660016446</v>
+        <v>0.001387400567830629</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.001731724097814755</v>
+        <v>0.0006235671599430169</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.0006001206631389422</v>
+        <v>0.001245676418371475</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.001003632199077672</v>
+        <v>0.0009840224086626742</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.002904632163810386</v>
+        <v>0.001238051291014417</v>
       </c>
       <c r="CP8" t="n">
-        <v>-5.396328322573029e-05</v>
+        <v>0.0002240105503843376</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.001282466884636113</v>
+        <v>0.00141060125163627</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.003546186032617352</v>
+        <v>0.002363203696851993</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.0003808195991204105</v>
+        <v>-0.0001046274901112282</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.0001179630314796759</v>
+        <v>0.001159176242740551</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0001660548989265376</v>
+        <v>1.665334536937735e-17</v>
       </c>
       <c r="CV8" t="n">
-        <v>0</v>
+        <v>2.215657311669949e-05</v>
       </c>
       <c r="CW8" t="n">
         <v>0</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.001101453643422848</v>
+        <v>0.0004961951367396994</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.001273108413611346</v>
+        <v>0.0003620927966314608</v>
       </c>
       <c r="CZ8" t="n">
-        <v>4.58435207824015e-05</v>
+        <v>0.0004736245759909802</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0004116703075930206</v>
+        <v>0.0002652780635066327</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.002100866399838261</v>
+        <v>0.001159828629200299</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.001530255558824362</v>
+        <v>0.000832014547633797</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0002324206629904124</v>
+        <v>0.0005899977819458363</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.002567746211507202</v>
+        <v>0.0006666029964260633</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.002059713117555778</v>
+        <v>0.0003192366985669714</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0006888016055896535</v>
+        <v>0.0002552247241585426</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.001168382717373562</v>
+        <v>0.0007560175475060604</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.001020566554514488</v>
+        <v>0.000688231173471937</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.001109641946653503</v>
+        <v>0.0001039775126481346</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.0001331483554311286</v>
+        <v>0.0003156867847747685</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.000140116216847716</v>
+        <v>0.0002291441033264119</v>
       </c>
       <c r="DM8" t="n">
-        <v>-4.420866489830422e-05</v>
+        <v>0.0004333939339750764</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.0007091894922740538</v>
+        <v>0.001302714405925742</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0004360185064596151</v>
+        <v>0.0005671777432895098</v>
       </c>
       <c r="DP8" t="n">
-        <v>-5.764828294283764e-05</v>
+        <v>0.0004849558827257933</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0001867193965636782</v>
+        <v>5.936121282658358e-05</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0001861147021728571</v>
+        <v>0.0001391220496947565</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.0001108402055203628</v>
+        <v>2.210433244915766e-05</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.0008806351212193919</v>
+        <v>0.001287564821301734</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.001123802433764942</v>
+        <v>0.0004011476958529963</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0003848146292769472</v>
+        <v>0.000791406360897845</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.0002960243947440516</v>
+        <v>0.0005501405108634727</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.001430163370292764</v>
+        <v>0.0007216153632799761</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.0001723875932142793</v>
+        <v>5.897096064781671e-05</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.0001065591415053163</v>
+        <v>0.0006192719618897307</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0002145475152892012</v>
+        <v>0.0005752737376701122</v>
       </c>
       <c r="EC8" t="n">
-        <v>6.177825651634827e-05</v>
+        <v>0.0007157888564728987</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.001006444831912912</v>
+        <v>0.0001769389560601964</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.0001108222084182292</v>
+        <v>3.088912825816859e-05</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0009620454089921904</v>
+        <v>0.0004291409441402493</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.001120720617045998</v>
+        <v>0.00070508977834787</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.000424080720232653</v>
+        <v>0.0001852926743323491</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.001124855903955951</v>
+        <v>0.0008040353737885836</v>
       </c>
       <c r="EJ8" t="n">
-        <v>-2.95967448443013e-05</v>
+        <v>0.0002730956742833968</v>
       </c>
       <c r="EK8" t="n">
-        <v>-0.0002185076491823951</v>
+        <v>-0.0003782034034807618</v>
       </c>
       <c r="EL8" t="n">
-        <v>2.350360388593542e-05</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.0001480462030216928</v>
+        <v>0.0004036575886490174</v>
       </c>
       <c r="EN8" t="n">
-        <v>0</v>
+        <v>0.0001547433642024698</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0003669776731070329</v>
+        <v>0.0002441814399017833</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0008172172703328207</v>
+        <v>0.000235835056568684</v>
       </c>
       <c r="ER8" t="n">
-        <v>0</v>
+        <v>4.439183190292906e-05</v>
       </c>
       <c r="ES8" t="n">
-        <v>3.087606038844337e-05</v>
+        <v>5.058766825704608e-05</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0008869940473854338</v>
+        <v>0.0002673946453410903</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.0006727556315661825</v>
+        <v>0.0002786256601959803</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.0002303847272948606</v>
+        <v>0.0001668258851148852</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0002505363341497535</v>
+        <v>-0.0001622855181431793</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0004750804830156719</v>
+        <v>8.118831098153644e-05</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.0003338490488810325</v>
+        <v>0.0005567942870047915</v>
       </c>
     </row>
     <row r="9">
@@ -4490,466 +4490,466 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003729238483234132</v>
+        <v>0.005770374776918541</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002757756189282412</v>
+        <v>0.002708153269951019</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002189570728896517</v>
+        <v>0.0009984399375975394</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002485942586564027</v>
+        <v>0.001942964587903495</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0007400828892835998</v>
+        <v>0.001041046995835848</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004997025580011949</v>
+        <v>0.004322084073416233</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001006214856466392</v>
+        <v>0.003151326053042147</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01082688875669249</v>
+        <v>0.002924667651403345</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003847292098253907</v>
+        <v>0.003627248599233335</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0007490636704119647</v>
+        <v>0.002391241717084402</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001378878094641234</v>
+        <v>0.001209082866411115</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002593575007368065</v>
+        <v>0.002740937223695816</v>
       </c>
       <c r="N9" t="n">
-        <v>0.00618679357525288</v>
+        <v>0.005800118976799562</v>
       </c>
       <c r="O9" t="n">
-        <v>0.005387496398732305</v>
+        <v>0.002932917316692685</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001189767995240965</v>
+        <v>0.002201070791195781</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.020464009518144</v>
+        <v>0.01142177275431295</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002230814991076746</v>
+        <v>0.001397977394408134</v>
       </c>
       <c r="S9" t="n">
-        <v>0.007376561570493811</v>
+        <v>0.003847292098253963</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001190849263553784</v>
+        <v>0.002679343128781342</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001516954193932218</v>
+        <v>0.001179593040401084</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001310452418096697</v>
+        <v>0.004867394695787852</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003353180821059265</v>
+        <v>0.0009507346585998167</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01071764337198374</v>
+        <v>0.01532434973362584</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001128172986524645</v>
+        <v>0.0006246281975015421</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002881014116969127</v>
+        <v>0.004609622587150653</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.007145095581322513</v>
+        <v>0.006808762581409111</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.002193669696020106</v>
+        <v>0.0009815585960738283</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.008447352766210647</v>
+        <v>0.002130993418990912</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.01615862681266645</v>
+        <v>0.01195620005918912</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.01918500892325999</v>
+        <v>0.02153480071386085</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01064842355740636</v>
+        <v>0.00919043503313165</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001391355831853158</v>
+        <v>0.002722699023379693</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.001992861392028567</v>
+        <v>0.003225806451612923</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.005358821685991911</v>
+        <v>0.008375258952352759</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.01475312314098756</v>
+        <v>0.0131669266770671</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.03682652457075192</v>
+        <v>0.02578448786264061</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.001378878094641223</v>
+        <v>0.001786228752520858</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.009399167162403365</v>
+        <v>0.00617784711388456</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.001684867394695755</v>
+        <v>0.00262304745063362</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.01281729865246009</v>
+        <v>0.006800376057662194</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.003447195236602985</v>
+        <v>0.001450562462995864</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.00365853658536589</v>
+        <v>0.002870514820592851</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.02138607971445573</v>
+        <v>0.01784651992861397</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.006863052334691355</v>
+        <v>0.003048239124001184</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.006925728611720505</v>
+        <v>0.004942290618526213</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.004937537180249885</v>
+        <v>0.004646345072506686</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.004735128736312521</v>
+        <v>0.001687388987566618</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.003854591037292432</v>
+        <v>0.0005022156573117331</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.001629583202757801</v>
+        <v>0.003301606186793626</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.005703541209652174</v>
+        <v>0.00198789974070872</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.004669382638671315</v>
+        <v>0.003063652587745447</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.01279000594884002</v>
+        <v>0.0071137574428079</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.01850089232599645</v>
+        <v>0.01115637731118771</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001629583202757789</v>
+        <v>0.001843849034860256</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0009048361934477223</v>
+        <v>0.0006050129645635005</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.002945785020369818</v>
+        <v>0.006675023503603894</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.007971445568114244</v>
+        <v>0.004967281380130917</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.003509871513632123</v>
+        <v>0.001946328516661788</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.003697900344719585</v>
+        <v>0.002538389219680371</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.03191552647233794</v>
+        <v>0.02079119571683528</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.006067816775728796</v>
+        <v>0.005383700178465234</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.005800118976799551</v>
+        <v>0.002270716602772083</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0007073386383730674</v>
+        <v>0.0007400828892836109</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.002593575007368065</v>
+        <v>0.002022605591909632</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.01071764337198377</v>
+        <v>0.005562165377751371</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.003823252898777863</v>
+        <v>0.003681747269890823</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.001222187402068364</v>
+        <v>0.001797819039198301</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.006988404888749644</v>
+        <v>0.00344719523660294</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.002558001189768022</v>
+        <v>0.003450327186198743</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.002427471876850185</v>
+        <v>0.004494382022471888</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.00526472337894115</v>
+        <v>0.002468768590124992</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.004263900893114336</v>
+        <v>0.001267646211466411</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0004461629982154047</v>
+        <v>0.0001253525540582778</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.001723597618301509</v>
+        <v>0.001411696917314875</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.002068317141961795</v>
+        <v>0.004350331316623423</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.00265053298761162</v>
+        <v>0.004937537180249885</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0005920663114268643</v>
+        <v>0.002161042036708116</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.002883108743340679</v>
+        <v>0.002929860905593362</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.002367564368156216</v>
+        <v>0.002071618822136723</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.003166617342408951</v>
+        <v>0.001901469317199633</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.002597799511002419</v>
+        <v>0.008863080684596547</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.00255850234009356</v>
+        <v>0.003065134099616818</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.001361349511689824</v>
+        <v>0.001786228752520891</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.003747769185008953</v>
+        <v>0.001397977394408145</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.001880288310874367</v>
+        <v>0.001784651992861419</v>
       </c>
       <c r="CJ9" t="n">
-        <v>8.862629246676468e-05</v>
+        <v>0.0001479727730097635</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.00300416418798336</v>
+        <v>0.003551346552234424</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.004982764023817021</v>
+        <v>0.002621722846441921</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.002309058614564818</v>
+        <v>0.002534630120836978</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.003361094586555635</v>
+        <v>0.003556942277691133</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.003361094586555635</v>
+        <v>0.00308892355694228</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0002368265245707657</v>
+        <v>0.0005327483547477585</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.003167554766133796</v>
+        <v>0.002161042036708083</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.004399375975038988</v>
+        <v>0.00466724286949004</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.001901469317199611</v>
+        <v>0.0005612998522895984</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.0009088060169226253</v>
+        <v>0.002681992337164729</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.001002063071028547</v>
+        <v>0.0005317577548006769</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.000414446417998815</v>
+        <v>0.0005327019828351487</v>
       </c>
       <c r="CW9" t="n">
         <v>0</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.002632403635224101</v>
+        <v>0.003197925669835777</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.007406305770374833</v>
+        <v>0.002592912705272232</v>
       </c>
       <c r="CZ9" t="n">
-        <v>9.401441554374168e-05</v>
+        <v>0.0005327483547477585</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0005918910920390541</v>
+        <v>0.0007436049970256265</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.004521118381915568</v>
+        <v>0.004180967238689581</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.002162331557505515</v>
+        <v>0.003140305387496378</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0006543723973825632</v>
+        <v>0.0008643042350907293</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.006038072575847741</v>
+        <v>0.002464898595943843</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.003831748775568966</v>
+        <v>0.001815038893690579</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.002082093991671674</v>
+        <v>0.001181683899556973</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.002328323017978151</v>
+        <v>0.002371294851794092</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.00462717359269077</v>
+        <v>0.001331754957087872</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.001526937481993629</v>
+        <v>0.0005304212168487088</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.00174607872151521</v>
+        <v>0.00127900059488405</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0002750611246943979</v>
+        <v>0.0003432137285491743</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0007834534628643585</v>
+        <v>0.001063515509601265</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.003124078986147916</v>
+        <v>0.004243369734789437</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.003572547790661274</v>
+        <v>0.002947244326554621</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.001974302726418087</v>
+        <v>0.004379994081089111</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.002130993418990956</v>
+        <v>0.0002368265245707657</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0004735128736312433</v>
+        <v>0.001699798329011815</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0002820432466312028</v>
+        <v>0.0007207771858351753</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.003384518959573846</v>
+        <v>0.00204202426753477</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.006719717064544595</v>
+        <v>0.001033973412112366</v>
       </c>
       <c r="DV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0.001840873634945406</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.002256345973049212</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>0.00319621189701097</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.0002016709881878187</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.001124593074874203</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0.002693104468777729</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>0.000951814396192785</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0.0006552262090483874</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>0.0001189767995241286</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>0.001390944066291777</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>0.002036979003447203</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0.0004164187983343726</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.00288101411696915</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>0.001029641185647456</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0.0006240249609984705</v>
+      </c>
+      <c r="EL9" t="n">
         <v>2.96033155713471e-05</v>
       </c>
-      <c r="DW9" t="n">
-        <v>0.0005304212168486533</v>
-      </c>
-      <c r="DX9" t="n">
-        <v>0.003450327186198732</v>
-      </c>
-      <c r="DY9" t="n">
-        <v>0.00408404853506954</v>
-      </c>
-      <c r="DZ9" t="n">
-        <v>0.001154446177847091</v>
-      </c>
-      <c r="EA9" t="n">
-        <v>0.001566906925728673</v>
-      </c>
-      <c r="EB9" t="n">
-        <v>0.0006483937518419914</v>
-      </c>
-      <c r="EC9" t="n">
-        <v>0.00156203949307393</v>
-      </c>
-      <c r="ED9" t="n">
-        <v>0.001992861392028577</v>
-      </c>
-      <c r="EE9" t="n">
-        <v>0.0003536693191865226</v>
-      </c>
-      <c r="EF9" t="n">
-        <v>0.002193669696020095</v>
-      </c>
-      <c r="EG9" t="n">
-        <v>0.001657295057709351</v>
-      </c>
-      <c r="EH9" t="n">
-        <v>0.000710269310446865</v>
-      </c>
-      <c r="EI9" t="n">
-        <v>0.002052349791790631</v>
-      </c>
-      <c r="EJ9" t="n">
-        <v>0.001516954193932218</v>
-      </c>
-      <c r="EK9" t="n">
-        <v>0.0009470257472624866</v>
-      </c>
-      <c r="EL9" t="n">
-        <v>0.0002676977989292895</v>
-      </c>
       <c r="EM9" t="n">
-        <v>0.0002072232089994186</v>
+        <v>0.0007490636704119647</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.0002184087363494291</v>
+        <v>0.0005327483547477363</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.0005651397977395112</v>
+        <v>0.0007962253022707477</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.001208370173887352</v>
+        <v>0.002726418050767809</v>
       </c>
       <c r="ER9" t="n">
-        <v>0</v>
+        <v>0.000265408434090264</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0002496099843993349</v>
+        <v>0.0006216696269982114</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.003196490128486429</v>
+        <v>0.0007077558242406523</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.00278909432779697</v>
+        <v>0.002681992337164707</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0006581009088060585</v>
+        <v>0.000438733939204039</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0009174311926605338</v>
+        <v>0.000828892835997641</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.001642178046672393</v>
+        <v>0.00143525741029642</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0007694584196507703</v>
+        <v>0.001479727730097635</v>
       </c>
     </row>
   </sheetData>
